--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="G2">
-        <v>406</v>
+        <v>193</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="G3">
-        <v>415</v>
+        <v>175</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D2">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E2">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D3">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="H3">
         <v>426</v>
